--- a/02_Шаблоны_и_Форматки/Шаблоны документов/СЗ_на_производство.xlsx
+++ b/02_Шаблоны_и_Форматки/Шаблоны документов/СЗ_на_производство.xlsx
@@ -16,9 +16,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Заготовка'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'1 Заготовка'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1 Заготовка'!$A$1:$H$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 Сварка'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2 Сварка'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2 Сварка'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 Покраска'!$1:$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3 Покраска'!$A$1:$F$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'4 Комплектация'!$1:$7</definedName>
@@ -654,17 +654,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -672,7 +672,7 @@
         <f>Данные!B1&amp;" | Производственная заявка"</f>
         <v/>
       </c>
-      <c r="G1" s="4">
+      <c r="H1" s="4">
         <f>"Дата: "&amp;Данные!B2</f>
         <v/>
       </c>
@@ -682,7 +682,7 @@
         <f>"№ заявки: "&amp;Данные!B3</f>
         <v/>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="4">
         <f>"Нач. КТО: "&amp;Данные!B4</f>
         <v/>
       </c>
@@ -692,7 +692,7 @@
         <f>"Изделие: "&amp;Данные!B5</f>
         <v/>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <f>"Шифр: "&amp;Данные!B6&amp;"  |  Кол-во: "&amp;Данные!B7&amp;" шт."</f>
         <v/>
       </c>
@@ -716,7 +716,7 @@
               <b val="1"/>
               <sz val="12"/>
             </rPr>
-            <t>1. ЦЕХ МЕТАЛЛОИЗДЕЛИЙ (Заготовительный участок: Резка, Гибка, ЧПУ-раскрой)</t>
+            <t>1. ЦЕХ МЕТАЛЛОИЗДЕЛИЙ (Заготовительный участок: лазерная резка, гибка)</t>
           </r>
         </is>
       </c>
@@ -724,7 +724,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Спецификация чистых заготовок на тираж (для ленточной пилы, ЧПУ-трубореза, трубогиба и лазера)</t>
+          <t>Спецификация чистых заготовок на тираж (лазерная резка листа и трубы, гибка)</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
         <f>IF(F8="","",F8*Данные!$B$7)</f>
         <v/>
       </c>
-      <c r="H8" s="9" t="n"/>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="8" t="n"/>
@@ -794,7 +794,7 @@
         <f>IF(F9="","",F9*Данные!$B$7)</f>
         <v/>
       </c>
-      <c r="H9" s="9" t="n"/>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="8" t="n"/>
@@ -807,7 +807,7 @@
         <f>IF(F10="","",F10*Данные!$B$7)</f>
         <v/>
       </c>
-      <c r="H10" s="9" t="n"/>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="8" t="n"/>
@@ -820,7 +820,7 @@
         <f>IF(F11="","",F11*Данные!$B$7)</f>
         <v/>
       </c>
-      <c r="H11" s="9" t="n"/>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="8" t="n"/>
@@ -833,7 +833,7 @@
         <f>IF(F12="","",F12*Данные!$B$7)</f>
         <v/>
       </c>
-      <c r="H12" s="9" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14">
@@ -864,45 +864,38 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="14.9" customHeight="1">
+    <row r="16" ht="26.8" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>•  Резка трубного проката выполняется ленточнопильным станком строго с охлаждением СОЖ. Погрешность по длине ±0.5 мм.</t>
+          <t>•  Трубы и профили резать на лазерном труборезе по файлам IGS, листовые детали — на лазере по чистому контуру DXF из папки 03_ЧПУ изделия.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14.9" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>•  Детали из листа вырезать на лазере по чистому контуру DXF из папки 03_ЧПУ изделия.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="14.9" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
           <t>•  Перед передачей в сварочный цех снять заусенцы на торцах всех заготовок и зачистить зоны сварных стыков.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Нач. КТО:</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>Начальник цеха металлоизделий:</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="22">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="22">
         <f>"____________________ / "&amp;Данные!B4</f>
         <v/>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>____________________ / ____________________</t>
         </is>
@@ -910,23 +903,22 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CC36"/>
-  <mergeCells count="17">
-    <mergeCell ref="A18:H18"/>
+  <mergeCells count="16">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E19:H19"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
     <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="H1"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="D3:H3"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -949,16 +941,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -966,7 +959,7 @@
         <f>Данные!B1&amp;" | Производственная заявка"</f>
         <v/>
       </c>
-      <c r="F1" s="4">
+      <c r="G1" s="4">
         <f>"Дата: "&amp;Данные!B2</f>
         <v/>
       </c>
@@ -976,7 +969,7 @@
         <f>"№ заявки: "&amp;Данные!B3</f>
         <v/>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <f>"Нач. КТО: "&amp;Данные!B4</f>
         <v/>
       </c>
@@ -1018,7 +1011,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Сборочные единицы металлокаркаса, нормативы сварки и масса конструкций</t>
+          <t>Сборочные единицы: сварная и механическая сборка, масса конструкций</t>
         </is>
       </c>
     </row>
@@ -1040,20 +1033,25 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>Операция</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>Масса 1 шт, кг</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>На 1 изд</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Всего на тираж</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Общая масса, кг</t>
         </is>
@@ -1063,14 +1061,15 @@
       <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="10" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="24">
-        <f>IF(E8="","",E8*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>IF(F8="","",D8*F8)</f>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="24">
+        <f>IF(F8="","",F8*Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IF(G8="","",E8*G8)</f>
         <v/>
       </c>
     </row>
@@ -1078,14 +1077,15 @@
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="10" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="24">
-        <f>IF(E9="","",E9*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G9" s="25">
-        <f>IF(F9="","",D9*F9)</f>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="24">
+        <f>IF(F9="","",F9*Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IF(G9="","",E9*G9)</f>
         <v/>
       </c>
     </row>
@@ -1093,14 +1093,15 @@
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="10" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="24">
-        <f>IF(E10="","",E10*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>IF(F10="","",D10*F10)</f>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="24">
+        <f>IF(F10="","",F10*Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IF(G10="","",E10*G10)</f>
         <v/>
       </c>
     </row>
@@ -1108,14 +1109,15 @@
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="10" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="24">
-        <f>IF(E11="","",E11*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>IF(F11="","",D11*F11)</f>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="24">
+        <f>IF(F11="","",F11*Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IF(G11="","",E11*G11)</f>
         <v/>
       </c>
     </row>
@@ -1123,36 +1125,38 @@
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="10" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="24">
-        <f>IF(E12="","",E12*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>IF(F12="","",D12*F12)</f>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="24">
+        <f>IF(F12="","",F12*Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IF(G12="","",E12*G12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>ИТОГО ГОТОВЫЙ МЕТАЛЛОКАРКАС НА ЗАКАЗ</t>
+          <t>ИТОГО СБОРОЧНЫХ ЕДИНИЦ НА ЗАКАЗ</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="15" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="17">
-        <f>SUM(E8:E12)</f>
-        <v/>
-      </c>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="26" t="n"/>
       <c r="F13" s="17">
         <f>SUM(F8:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="17">
         <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>SUM(H8:H12)</f>
         <v/>
       </c>
     </row>
@@ -1170,7 +1174,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="26.8" customHeight="1">
+    <row r="17" ht="14.9" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t>•  Сварные швы сплошные, катет шва 2.0...3.0 мм. Не допускаются непровары, прожоги тонкостенных труб и наплывы металла.</t>
@@ -1210,23 +1214,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CC36"/>
   <mergeCells count="17">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1833,7 +1837,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Расчет потребности в хлыстах 6000 мм, КИМ, деловых обрезков (&gt;=500 мм) и технологического отхода</t>
+          <t>Расчет потребности в хлыстах, КИМ, деловых обрезков и технологического отхода по справочнику «Нормативы производства»</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Хлыстов 6 м</t>
+          <t>Хлыстов</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Деловые обрезки (&gt;=500 мм)</t>
+          <t>Деловые обрезки</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1976,7 +1980,7 @@
     <row r="16" ht="14.9" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>•  Технологический отход металла (стружка, торцовка и обрезки &lt;500 мм) подлежит сдаче в металлолом.</t>
+          <t>•  Технологический отход металла (торцовка, рез и обрезки короче делового) подлежит сдаче в металлолом.</t>
         </is>
       </c>
     </row>

--- a/02_Шаблоны_и_Форматки/Шаблоны документов/СЗ_на_производство.xlsx
+++ b/02_Шаблоны_и_Форматки/Шаблоны документов/СЗ_на_производство.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 Сварка'!$1:$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2 Сварка'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 Покраска'!$1:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'3 Покраска'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'3 Покраска'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'4 Комплектация'!$1:$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'4 Комплектация'!$A$1:$G$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'5 Списание'!$1:$7</definedName>
@@ -131,11 +131,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1252,15 +1256,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1268,7 +1274,7 @@
         <f>Данные!B1&amp;" | Производственная заявка"</f>
         <v/>
       </c>
-      <c r="E1" s="4">
+      <c r="G1" s="4">
         <f>"Дата: "&amp;Данные!B2</f>
         <v/>
       </c>
@@ -1278,7 +1284,7 @@
         <f>"№ заявки: "&amp;Данные!B3</f>
         <v/>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <f>"Нач. КТО: "&amp;Данные!B4</f>
         <v/>
       </c>
@@ -1288,7 +1294,7 @@
         <f>"Изделие: "&amp;Данные!B5</f>
         <v/>
       </c>
-      <c r="C3" s="4">
+      <c r="D3" s="4">
         <f>"Шифр: "&amp;Данные!B6&amp;"  |  Кол-во: "&amp;Данные!B7&amp;" шт."</f>
         <v/>
       </c>
@@ -1320,7 +1326,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ведомость окрашиваемых сборочных единиц и цвет полимерного покрытия</t>
+          <t>Ведомость окрашиваемых единиц по цветовым исполнениям заказа</t>
         </is>
       </c>
     </row>
@@ -1342,15 +1348,25 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>Цветовое исполнение</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Изделий</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
           <t>На 1 изд</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Всего на тираж</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Цвет покрытия</t>
         </is>
@@ -1360,56 +1376,81 @@
       <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="10" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="10" t="n"/>
       <c r="E8" s="24">
-        <f>IF(D8="","",D8*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="9" t="n"/>
+        <f>IF(B8="","",Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="24">
+        <f>IF(F8="","",E8*F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="10" t="n"/>
-      <c r="D9" s="12" t="n"/>
+      <c r="D9" s="10" t="n"/>
       <c r="E9" s="24">
-        <f>IF(D9="","",D9*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9" t="n"/>
+        <f>IF(B9="","",Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="24">
+        <f>IF(F9="","",E9*F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="10" t="n"/>
-      <c r="D10" s="12" t="n"/>
+      <c r="D10" s="10" t="n"/>
       <c r="E10" s="24">
-        <f>IF(D10="","",D10*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F10" s="9" t="n"/>
+        <f>IF(B10="","",Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="24">
+        <f>IF(F10="","",E10*F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="10" t="n"/>
-      <c r="D11" s="12" t="n"/>
+      <c r="D11" s="10" t="n"/>
       <c r="E11" s="24">
-        <f>IF(D11="","",D11*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F11" s="9" t="n"/>
+        <f>IF(B11="","",Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="24">
+        <f>IF(F11="","",E11*F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="10" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="10" t="n"/>
       <c r="E12" s="24">
-        <f>IF(D12="","",D12*Данные!$B$7)</f>
-        <v/>
-      </c>
-      <c r="F12" s="9" t="n"/>
+        <f>IF(B12="","",Данные!$B$7)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="24">
+        <f>IF(F12="","",E12*F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -1419,15 +1460,17 @@
       </c>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="15" t="n"/>
-      <c r="D13" s="17">
-        <f>SUM(D8:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="17">
-        <f>SUM(E8:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="18" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="17">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
@@ -1463,7 +1506,7 @@
           <t>Нач. КТО:</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>Мастер малярного участка:</t>
         </is>
@@ -1474,7 +1517,7 @@
         <f>"____________________ / "&amp;Данные!B4</f>
         <v/>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>____________________ / ____________________</t>
         </is>
@@ -1483,23 +1526,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CC36"/>
   <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.5" footer="0.5"/>
